--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-research-study-category-cs.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-research-study-category-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T19:23:22+00:00</t>
+    <t>2026-08-31T19:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-research-study-category-cs.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-research-study-category-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T19:27:08+00:00</t>
+    <t>2026-08-31T20:04:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-research-study-category-cs.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-research-study-category-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:04:18+00:00</t>
+    <t>2026-08-31T20:08:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-research-study-category-cs.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-research-study-category-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:08:28+00:00</t>
+    <t>2026-08-31T20:26:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
